--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_6.xlsx
@@ -513,1376 +513,1376 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_0</t>
+          <t>model_23_6_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9982592845190723</v>
+        <v>0.995382930213466</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7728440878118857</v>
+        <v>0.7227957891217698</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9984246187987137</v>
+        <v>0.9421693267074515</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9944846004306593</v>
+        <v>0.9855723483392339</v>
       </c>
       <c r="F2" t="n">
-        <v>0.997394153482422</v>
+        <v>0.975625055360863</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01164017243622124</v>
+        <v>0.002740892072316326</v>
       </c>
       <c r="H2" t="n">
-        <v>1.51899263075872</v>
+        <v>0.1645603941757199</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01650248263108131</v>
+        <v>0.01018316902206635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05624859164375982</v>
+        <v>0.006924745656786516</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03637556523620709</v>
+        <v>0.008553955624749175</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2443608981956184</v>
+        <v>0.03158286947686299</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1078896308095511</v>
+        <v>0.05235352970255517</v>
       </c>
       <c r="N2" t="n">
-        <v>1.00097156212889</v>
+        <v>1.002130955286093</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1124827157554383</v>
+        <v>0.05458232784873975</v>
       </c>
       <c r="P2" t="n">
-        <v>142.9065860453604</v>
+        <v>163.7989436754635</v>
       </c>
       <c r="Q2" t="n">
-        <v>224.5712663115299</v>
+        <v>256.4335063654468</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_1</t>
+          <t>model_23_6_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9982592629731372</v>
+        <v>0.9954441804135784</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7728438616759038</v>
+        <v>0.7227370571857203</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9984246514590389</v>
+        <v>0.9429608352866936</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9944844785332462</v>
+        <v>0.9857665215371478</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9973941248179845</v>
+        <v>0.975956409090837</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01164031651398891</v>
+        <v>0.002704531307658722</v>
       </c>
       <c r="H3" t="n">
-        <v>1.518994142931072</v>
+        <v>0.1645952599900465</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0165021405066172</v>
+        <v>0.01004379548228299</v>
       </c>
       <c r="J3" t="n">
-        <v>0.05624983480986807</v>
+        <v>0.00683154961625729</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03637596536918047</v>
+        <v>0.008437672894910998</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2443585692639102</v>
+        <v>0.03144274041876109</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1078902985165437</v>
+        <v>0.05200510847655951</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000971574154528</v>
+        <v>1.002102685962964</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1124834118880999</v>
+        <v>0.0542190736098221</v>
       </c>
       <c r="P3" t="n">
-        <v>142.9065612902502</v>
+        <v>163.8256533011684</v>
       </c>
       <c r="Q3" t="n">
-        <v>224.5712415564196</v>
+        <v>256.4602159911516</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_2</t>
+          <t>model_23_6_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9982591364580005</v>
+        <v>0.9955115190824761</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7728429188109562</v>
+        <v>0.7226712717467861</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9984247850456788</v>
+        <v>0.9438333934092382</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9944838226325913</v>
+        <v>0.98598062328092</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9973939394400581</v>
+        <v>0.9763217218272521</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01164116252129061</v>
+        <v>0.002664556164922007</v>
       </c>
       <c r="H4" t="n">
-        <v>1.519000447873318</v>
+        <v>0.1646343130683808</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01650074115565158</v>
+        <v>0.009890150256703471</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05625652398762111</v>
+        <v>0.006728788601841578</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03637855309904676</v>
+        <v>0.008309472852502163</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2443367007557006</v>
+        <v>0.03128719268965331</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1078942191282305</v>
+        <v>0.05161933905932937</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000971644767628</v>
+        <v>1.002071606577319</v>
       </c>
       <c r="O4" t="n">
-        <v>0.112487499408343</v>
+        <v>0.05381688118984768</v>
       </c>
       <c r="P4" t="n">
-        <v>142.9064159374054</v>
+        <v>163.8554355549544</v>
       </c>
       <c r="Q4" t="n">
-        <v>224.5710962035748</v>
+        <v>256.4899982449376</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_3</t>
+          <t>model_23_6_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9982590988412734</v>
+        <v>0.995585444801006</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7728425665333924</v>
+        <v>0.7225978257820546</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9984248383865635</v>
+        <v>0.9447941710611026</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9944836136481763</v>
+        <v>0.9862164781733773</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9973938783202999</v>
+        <v>0.9767240713023051</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01164141406451786</v>
+        <v>0.002620670664977916</v>
       </c>
       <c r="H5" t="n">
-        <v>1.519002803555009</v>
+        <v>0.1646779137657459</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01650018239754178</v>
+        <v>0.009720970811531424</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05625865530718684</v>
+        <v>0.006615586870847698</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03637940628273657</v>
+        <v>0.008168275421853697</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2443296818012175</v>
+        <v>0.03111448660344183</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1078953848156531</v>
+        <v>0.05119248641136623</v>
       </c>
       <c r="N5" t="n">
-        <v>1.00097166576301</v>
+        <v>1.00203748701492</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1124887147214925</v>
+        <v>0.05337185654095396</v>
       </c>
       <c r="P5" t="n">
-        <v>142.9063727217027</v>
+        <v>163.8886500299339</v>
       </c>
       <c r="Q5" t="n">
-        <v>224.5710529878721</v>
+        <v>256.5232127199172</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_4</t>
+          <t>model_23_6_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9982590992541958</v>
+        <v>0.9956665071927299</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7728424998775685</v>
+        <v>0.7225151960702291</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9984248420544952</v>
+        <v>0.9458515031065877</v>
       </c>
       <c r="E6" t="n">
-        <v>0.994483611567878</v>
+        <v>0.9864760377447366</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9973938766488523</v>
+        <v>0.9771668304831412</v>
       </c>
       <c r="G6" t="n">
-        <v>0.011641411303304</v>
+        <v>0.002572548527537622</v>
       </c>
       <c r="H6" t="n">
-        <v>1.519003249282811</v>
+        <v>0.1647269663321032</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01650014397510808</v>
+        <v>0.009534789494271714</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05625867652302954</v>
+        <v>0.006491007760074196</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03637942961483001</v>
+        <v>0.008012896919814287</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2443274675402621</v>
+        <v>0.03092264299980457</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1078953720198601</v>
+        <v>0.05072029699772688</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000971665532542</v>
+        <v>1.002000073603355</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1124887013809561</v>
+        <v>0.05287956504640914</v>
       </c>
       <c r="P6" t="n">
-        <v>142.9063731960805</v>
+        <v>163.9257164529476</v>
       </c>
       <c r="Q6" t="n">
-        <v>224.5710534622499</v>
+        <v>256.5602791429308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_5</t>
+          <t>model_23_6_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9982590891342199</v>
+        <v>0.9957552234346676</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7728424021769651</v>
+        <v>0.7224226571237342</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9984248558284742</v>
+        <v>0.9470130889309663</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9944835559443089</v>
+        <v>0.9867613981444792</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9973938569853342</v>
+        <v>0.9776533936940337</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01164147897562903</v>
+        <v>0.002519882733981257</v>
       </c>
       <c r="H7" t="n">
-        <v>1.519003902607196</v>
+        <v>0.1647819014482169</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01649999968949048</v>
+        <v>0.009330250551357368</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05625924379787203</v>
+        <v>0.006354045194356735</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03637970410205563</v>
+        <v>0.007842146168326344</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2443270283226174</v>
+        <v>0.03070968637306267</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1078956856210156</v>
+        <v>0.05019843358095208</v>
       </c>
       <c r="N7" t="n">
-        <v>1.0009716711809</v>
+        <v>1.001959127645538</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1124890283327621</v>
+        <v>0.05233548482357604</v>
       </c>
       <c r="P7" t="n">
-        <v>142.9063615699766</v>
+        <v>163.9670858253519</v>
       </c>
       <c r="Q7" t="n">
-        <v>224.571041836146</v>
+        <v>256.6016485153352</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_6</t>
+          <t>model_23_6_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9982590812328676</v>
+        <v>0.9958521870472484</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7728423627962243</v>
+        <v>0.7223184929145062</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9984248638176459</v>
+        <v>0.948288500018539</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9944835153571333</v>
+        <v>0.9870747897641911</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9973938561241136</v>
+        <v>0.9781876782599872</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0116415318120085</v>
+        <v>0.002462320944943337</v>
       </c>
       <c r="H8" t="n">
-        <v>1.519004165946391</v>
+        <v>0.1648437378224742</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01649991600106782</v>
+        <v>0.009105668578886299</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05625965772463135</v>
+        <v>0.006203628667225404</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03637971612401897</v>
+        <v>0.007654648451477536</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2443258614536371</v>
+        <v>0.03047319040576657</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1078959304700993</v>
+        <v>0.0496217789377138</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000971675590958</v>
+        <v>1.001914375208962</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1124892836055782</v>
+        <v>0.05173428079833543</v>
       </c>
       <c r="P8" t="n">
-        <v>142.9063524927349</v>
+        <v>164.0133018005502</v>
       </c>
       <c r="Q8" t="n">
-        <v>224.5710327589043</v>
+        <v>256.6478644905334</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_8</t>
+          <t>model_23_6_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9982590512774008</v>
+        <v>0.9959579250936158</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7728422132870807</v>
+        <v>0.7222014799079302</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9984248746375071</v>
+        <v>0.9496866814081116</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9944833814766624</v>
+        <v>0.9874183915766425</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9973938114166842</v>
+        <v>0.9787734314855819</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01164173212435243</v>
+        <v>0.002399550272973864</v>
       </c>
       <c r="H9" t="n">
-        <v>1.519005165714723</v>
+        <v>0.1649132017978764</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01649980266051928</v>
+        <v>0.008859468481206308</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05626102309949573</v>
+        <v>0.006038712351363218</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03638034020452482</v>
+        <v>0.007449088719015802</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2443230442591433</v>
+        <v>0.03021034950199678</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1078968587325527</v>
+        <v>0.04898520463337746</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000971692310288</v>
+        <v>1.001865573033716</v>
       </c>
       <c r="O9" t="n">
-        <v>0.112490251386086</v>
+        <v>0.05107060620797303</v>
       </c>
       <c r="P9" t="n">
-        <v>142.9063180796312</v>
+        <v>164.0649478908963</v>
       </c>
       <c r="Q9" t="n">
-        <v>224.5709983458006</v>
+        <v>256.6995105808795</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_7</t>
+          <t>model_23_6_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9982590565892346</v>
+        <v>0.9960729668482527</v>
       </c>
       <c r="C10" t="n">
-        <v>0.772842210958113</v>
+        <v>0.7220696602099814</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9984248794441802</v>
+        <v>0.9512171958212217</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9944833983076787</v>
+        <v>0.9877945660027997</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9973938120812337</v>
+        <v>0.9794146501151573</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01164169660409563</v>
+        <v>0.002331256517876362</v>
       </c>
       <c r="H10" t="n">
-        <v>1.51900518128854</v>
+        <v>0.1649914556648933</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01649975230950553</v>
+        <v>0.008589966397414795</v>
       </c>
       <c r="J10" t="n">
-        <v>0.05626085144901846</v>
+        <v>0.005858162371021614</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03638033092793709</v>
+        <v>0.007224064384218205</v>
       </c>
       <c r="L10" t="n">
-        <v>0.244321864334052</v>
+        <v>0.02991846498114697</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1078966941295962</v>
+        <v>0.04828308728609183</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000971689345543</v>
+        <v>1.001812476839268</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1124900797756408</v>
+        <v>0.05033859827163016</v>
       </c>
       <c r="P10" t="n">
-        <v>142.9063241818693</v>
+        <v>164.1226957574083</v>
       </c>
       <c r="Q10" t="n">
-        <v>224.5710044480388</v>
+        <v>256.7572584473916</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_11</t>
+          <t>model_23_6_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9982590529820874</v>
+        <v>0.9961977046246905</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7728422103745791</v>
+        <v>0.721921257215995</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9984248886982148</v>
+        <v>0.9528882316221279</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9882054575991192</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9973938107752237</v>
+        <v>0.9801148690885318</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01164172072510524</v>
+        <v>0.002257206785391548</v>
       </c>
       <c r="H11" t="n">
-        <v>1.519005185190634</v>
+        <v>0.1650795540927992</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01649965537135195</v>
+        <v>0.008295720471615683</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.005660949417456881</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03638034915880814</v>
+        <v>0.006978334922489019</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2443231378113558</v>
+        <v>0.02959443244563081</v>
       </c>
       <c r="M11" t="n">
-        <v>0.107896805907799</v>
+        <v>0.04751007035767835</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000971691358835</v>
+        <v>1.001754905557835</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1124901963124731</v>
+        <v>0.0495326724122085</v>
       </c>
       <c r="P11" t="n">
-        <v>142.9063200379743</v>
+        <v>164.1872543315276</v>
       </c>
       <c r="Q11" t="n">
-        <v>224.5710003041437</v>
+        <v>256.8218170215108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_12</t>
+          <t>model_23_6_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9982590529820874</v>
+        <v>0.9963325218662191</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7728422103745791</v>
+        <v>0.7217537179430635</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9984248886982148</v>
+        <v>0.9547089536822875</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9886533384059042</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9973938107752237</v>
+        <v>0.9808779411928844</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01164172072510524</v>
+        <v>0.002177173447018582</v>
       </c>
       <c r="H12" t="n">
-        <v>1.519005185190634</v>
+        <v>0.165179012642531</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01649965537135195</v>
+        <v>0.007975116898715554</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.005445982994336401</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03638034915880814</v>
+        <v>0.006710548266324253</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2443231378113558</v>
+        <v>0.02923464718575955</v>
       </c>
       <c r="M12" t="n">
-        <v>0.107896805907799</v>
+        <v>0.04666019124498507</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000971691358835</v>
+        <v>1.001692682215591</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1124901963124731</v>
+        <v>0.04864661218619556</v>
       </c>
       <c r="P12" t="n">
-        <v>142.9063200379743</v>
+        <v>164.2594556548196</v>
       </c>
       <c r="Q12" t="n">
-        <v>224.5710003041437</v>
+        <v>256.8940183448029</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_10</t>
+          <t>model_23_6_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9982590529820874</v>
+        <v>0.9964776466407381</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7728422103745791</v>
+        <v>0.7215646252474304</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9984248886982148</v>
+        <v>0.9566872036406343</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9891403939563584</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9973938107752237</v>
+        <v>0.9817073018208322</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01164172072510524</v>
+        <v>0.002091021111800267</v>
       </c>
       <c r="H13" t="n">
-        <v>1.519005185190634</v>
+        <v>0.165291266235038</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01649965537135195</v>
+        <v>0.007626774876276454</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.005212214125574925</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03638034915880814</v>
+        <v>0.006419498825457463</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2443231378113558</v>
+        <v>0.02883536648285853</v>
       </c>
       <c r="M13" t="n">
-        <v>0.107896805907799</v>
+        <v>0.04572768430393417</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000971691358835</v>
+        <v>1.001625701550429</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1124901963124731</v>
+        <v>0.04767440649410863</v>
       </c>
       <c r="P13" t="n">
-        <v>142.9063200379743</v>
+        <v>164.3402055241553</v>
       </c>
       <c r="Q13" t="n">
-        <v>224.5710003041437</v>
+        <v>256.9747682141385</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_9</t>
+          <t>model_23_6_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9982590540899667</v>
+        <v>0.9966332249758301</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7728422072129224</v>
+        <v>0.7213505603743549</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9984248874743694</v>
+        <v>0.958831909694567</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9944833798174582</v>
+        <v>0.9896684530522726</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9973938117400433</v>
+        <v>0.9826064923009707</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01164171331671139</v>
+        <v>0.001998663091455523</v>
       </c>
       <c r="H14" t="n">
-        <v>1.519005206332647</v>
+        <v>0.1654183443908166</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01649966819141541</v>
+        <v>0.007249122274181298</v>
       </c>
       <c r="J14" t="n">
-        <v>0.05626104002082575</v>
+        <v>0.00495876505313149</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03638033569068672</v>
+        <v>0.006103943833264711</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2443225450452837</v>
+        <v>0.02839188190028196</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1078967715768706</v>
+        <v>0.04470640995937297</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000971690740484</v>
+        <v>1.001553896165001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.112490160520006</v>
+        <v>0.04660965438637013</v>
       </c>
       <c r="P14" t="n">
-        <v>142.9063213107064</v>
+        <v>164.4305535524192</v>
       </c>
       <c r="Q14" t="n">
-        <v>224.5710015768759</v>
+        <v>257.0651162424024</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_23</t>
+          <t>model_23_6_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9967990568358261</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7211078651395348</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9611479417557609</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9902392100864842</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9835778709144942</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.00190021813579851</v>
       </c>
       <c r="H15" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1655624187660941</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.006841301569408349</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.004684822530351797</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.005763055692679199</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.02789954742702644</v>
       </c>
       <c r="M15" t="n">
-        <v>0.107896791547543</v>
+        <v>0.04359149155280776</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000971691100185</v>
+        <v>1.001477358383465</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.04544727159503817</v>
       </c>
       <c r="P15" t="n">
-        <v>142.9063205703443</v>
+        <v>164.5315731821694</v>
       </c>
       <c r="Q15" t="n">
-        <v>224.5710008365137</v>
+        <v>257.1661358721527</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_13</t>
+          <t>model_23_6_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9969745800136168</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7208326714010008</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9636382603297422</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9908534173773422</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9846226560568869</v>
       </c>
       <c r="G16" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.001796019995255471</v>
       </c>
       <c r="H16" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1657257856570384</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.006402791458530711</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.004390025471915623</v>
       </c>
       <c r="K16" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.00539640682935931</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.02735339464397693</v>
       </c>
       <c r="M16" t="n">
-        <v>0.107896791547543</v>
+        <v>0.04237947610878963</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000971691100185</v>
+        <v>1.001396347686023</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.04418365814435034</v>
       </c>
       <c r="P16" t="n">
-        <v>142.9063205703443</v>
+        <v>164.6443643518967</v>
       </c>
       <c r="Q16" t="n">
-        <v>224.5710008365137</v>
+        <v>257.27892704188</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_14</t>
+          <t>model_23_6_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9971590599807949</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7205195263632846</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9663060447607792</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9915117568501219</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9857421617690864</v>
       </c>
       <c r="G17" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.001686504717618939</v>
       </c>
       <c r="H17" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1659116820785879</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.005933032103693893</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.004074046578606212</v>
       </c>
       <c r="K17" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.00500353610388366</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.02674674970877325</v>
       </c>
       <c r="M17" t="n">
-        <v>0.107896791547543</v>
+        <v>0.0410670758347723</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000971691100185</v>
+        <v>1.001311203085787</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.04281538627362501</v>
       </c>
       <c r="P17" t="n">
-        <v>142.9063205703443</v>
+        <v>164.7701942123656</v>
       </c>
       <c r="Q17" t="n">
-        <v>224.5710008365137</v>
+        <v>257.4047569023488</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_15</t>
+          <t>model_23_6_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9973509899399806</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7201625931795006</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9691467950928072</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9922135841186828</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9869347775199883</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.001572566802903737</v>
       </c>
       <c r="H18" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1661235730351929</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.005432815883934627</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.003737195132227245</v>
       </c>
       <c r="K18" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.004585008703652681</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.02607309478714911</v>
       </c>
       <c r="M18" t="n">
-        <v>0.107896791547543</v>
+        <v>0.03965560241509056</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000971691100185</v>
+        <v>1.001222620027701</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.04134382350831464</v>
       </c>
       <c r="P18" t="n">
-        <v>142.9063205703443</v>
+        <v>164.9100921766365</v>
       </c>
       <c r="Q18" t="n">
-        <v>224.5710008365137</v>
+        <v>257.5446548666197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_16</t>
+          <t>model_23_6_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9975481118771349</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7197552480231568</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9721508512163155</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9929565753712778</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9881965364843407</v>
       </c>
       <c r="G19" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.001455546705784704</v>
       </c>
       <c r="H19" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1663653907163931</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.004903843808809223</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.003380586477512565</v>
       </c>
       <c r="K19" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.00414221671581487</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.02532538434295219</v>
       </c>
       <c r="M19" t="n">
-        <v>0.107896791547543</v>
+        <v>0.03815162782614529</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000971691100185</v>
+        <v>1.001131640672092</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.03977582160746138</v>
       </c>
       <c r="P19" t="n">
-        <v>142.9063205703443</v>
+        <v>165.0647474122499</v>
       </c>
       <c r="Q19" t="n">
-        <v>224.5710008365137</v>
+        <v>257.6993101022332</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_17</t>
+          <t>model_23_6_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9977473647264978</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7192890432484356</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.975301854871892</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9937371801527323</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9895208923985346</v>
       </c>
       <c r="G20" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.001337261607127926</v>
       </c>
       <c r="H20" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1666421500096653</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.004348996337959889</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.003005924703223716</v>
       </c>
       <c r="K20" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.00367745743577946</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.02449525351571977</v>
       </c>
       <c r="M20" t="n">
-        <v>0.107896791547543</v>
+        <v>0.03656858771032764</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000971691100185</v>
+        <v>1.00103967781854</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.03812538819656856</v>
       </c>
       <c r="P20" t="n">
-        <v>142.9063205703443</v>
+        <v>165.2342626654834</v>
       </c>
       <c r="Q20" t="n">
-        <v>224.5710008365137</v>
+        <v>257.8688253554666</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_18</t>
+          <t>model_23_6_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9979444676064523</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7187542952518812</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9785737428057425</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9945494588914618</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9908972013853251</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.001220252823185899</v>
       </c>
       <c r="H21" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1669595995203306</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.003772862844180355</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.002616060586708228</v>
       </c>
       <c r="K21" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.00319446614397373</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.02357332281412302</v>
       </c>
       <c r="M21" t="n">
-        <v>0.107896791547543</v>
+        <v>0.03493211735904222</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000971691100185</v>
+        <v>1.000948707258561</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.03641924991446829</v>
       </c>
       <c r="P21" t="n">
-        <v>142.9063205703443</v>
+        <v>165.417394419174</v>
       </c>
       <c r="Q21" t="n">
-        <v>224.5710008365137</v>
+        <v>258.0519571091572</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_19</t>
+          <t>model_23_6_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9981336358695565</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7181390699169045</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9819272009283739</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.99538471931913</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9923097282985365</v>
       </c>
       <c r="G22" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.001107954370563748</v>
       </c>
       <c r="H22" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1673248238555234</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.00318236598625121</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.002215166099179882</v>
       </c>
       <c r="K22" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.002698764811591049</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.02254866942859946</v>
       </c>
       <c r="M22" t="n">
-        <v>0.107896791547543</v>
+        <v>0.03328594854535091</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000971691100185</v>
+        <v>1.000861398829435</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.03470300028633892</v>
       </c>
       <c r="P22" t="n">
-        <v>142.9063205703443</v>
+        <v>165.6104797466134</v>
       </c>
       <c r="Q22" t="n">
-        <v>224.5710008365137</v>
+        <v>258.2450424365967</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_20</t>
+          <t>model_23_6_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.998307181099953</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7174290037572639</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9853076639334034</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.996230054772665</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9937358923214306</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.001004930425036784</v>
       </c>
       <c r="H23" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1677463498011471</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.00258711394796147</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.001809435967344721</v>
       </c>
       <c r="K23" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.00219827777680772</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.02140898010582652</v>
       </c>
       <c r="M23" t="n">
-        <v>0.107896791547543</v>
+        <v>0.03170063761246427</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000971691100185</v>
+        <v>1.000781301030791</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.03305019938499326</v>
       </c>
       <c r="P23" t="n">
-        <v>142.9063205703443</v>
+        <v>165.8056739373733</v>
       </c>
       <c r="Q23" t="n">
-        <v>224.5710008365137</v>
+        <v>258.4402366273566</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_21</t>
+          <t>model_23_6_2</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9984547241614634</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7166069331183824</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9886344905054552</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9970676185822492</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9951433170353889</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.000917342490195827</v>
       </c>
       <c r="H24" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1682343664439896</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.002001306531905158</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.001407435940654859</v>
       </c>
       <c r="K24" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.00170436697099422</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.02014075377625237</v>
       </c>
       <c r="M24" t="n">
-        <v>0.107896791547543</v>
+        <v>0.03028766234287201</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000971691100185</v>
+        <v>1.000713204233171</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.03157707083291243</v>
       </c>
       <c r="P24" t="n">
-        <v>142.9063205703443</v>
+        <v>165.9880593311682</v>
       </c>
       <c r="Q24" t="n">
-        <v>224.5710008365137</v>
+        <v>258.6226220211515</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_22</t>
+          <t>model_23_6_1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9985628080260398</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.715651903249341</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9918004583997146</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9978728733405384</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9964882548258959</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.0008531792392034326</v>
       </c>
       <c r="H25" t="n">
-        <v>1.519005207442714</v>
+        <v>0.1688013134293948</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.001443824068877462</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.001020943078116934</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.001232384845563175</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.01872772953289324</v>
       </c>
       <c r="M25" t="n">
-        <v>0.107896791547543</v>
+        <v>0.02920923208856119</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000971691100185</v>
+        <v>1.000663319372597</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.03045272957001721</v>
       </c>
       <c r="P25" t="n">
-        <v>142.9063205703443</v>
+        <v>166.1330818090472</v>
       </c>
       <c r="Q25" t="n">
-        <v>224.5710008365137</v>
+        <v>258.7676444990305</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_24</t>
+          <t>model_23_6_0</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9982590534455014</v>
+        <v>0.9986138377580389</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7728422070469189</v>
+        <v>0.7145367154927298</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9984248905469386</v>
+        <v>0.9946602525369039</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9944833740202981</v>
+        <v>0.9986128885085277</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9973938103590293</v>
+        <v>0.9977117876742508</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01164171762625394</v>
+        <v>0.0008228857859191012</v>
       </c>
       <c r="H26" t="n">
-        <v>1.519005207442714</v>
+        <v>0.169463337055322</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0164996360055419</v>
+        <v>0.0009402545026025727</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0562610991429421</v>
+        <v>0.0006657628352763536</v>
       </c>
       <c r="K26" t="n">
-        <v>0.03638035496855381</v>
+        <v>0.0008030076369090545</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2443224062650272</v>
+        <v>0.0171526815298173</v>
       </c>
       <c r="M26" t="n">
-        <v>0.107896791547543</v>
+        <v>0.02868598588020117</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000971691100185</v>
+        <v>1.000639767188597</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1124901813408713</v>
+        <v>0.02990720768729834</v>
       </c>
       <c r="P26" t="n">
-        <v>142.9063205703443</v>
+        <v>166.2053862893176</v>
       </c>
       <c r="Q26" t="n">
-        <v>224.5710008365137</v>
+        <v>258.8399489793009</v>
       </c>
     </row>
   </sheetData>

--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_6.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_24</t>
+          <t>model_23_6_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.995382930213466</v>
+        <v>0.9999785821497486</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7227957891217698</v>
+        <v>0.71097939410263</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9421693267074515</v>
+        <v>0.9999991314728619</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9855723483392339</v>
+        <v>0.9999438134207271</v>
       </c>
       <c r="F2" t="n">
-        <v>0.975625055360863</v>
+        <v>0.9999752934326784</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002740892072316326</v>
+        <v>1.271456111220114e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1645603941757199</v>
+        <v>0.1715751167007679</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01018316902206635</v>
+        <v>4.433190162542302e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.006924745656786516</v>
+        <v>2.179555477457088e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008553955624749175</v>
+        <v>1.111944579275607e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03158286947686299</v>
+        <v>0.001296995715624917</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05235352970255517</v>
+        <v>0.003565748324293393</v>
       </c>
       <c r="N2" t="n">
-        <v>1.002130955286093</v>
+        <v>1.000009885161655</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05458232784873975</v>
+        <v>0.003717549612575165</v>
       </c>
       <c r="P2" t="n">
-        <v>163.7989436754635</v>
+        <v>174.5455253540237</v>
       </c>
       <c r="Q2" t="n">
-        <v>256.4335063654468</v>
+        <v>267.1800880440069</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_23</t>
+          <t>model_23_6_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9954441804135784</v>
+        <v>0.9999817948457441</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7227370571857203</v>
+        <v>0.7106605989095537</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9429608352866936</v>
+        <v>0.9999961053354786</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9857665215371478</v>
+        <v>0.9999505462317239</v>
       </c>
       <c r="F3" t="n">
-        <v>0.975956409090837</v>
+        <v>0.9999764789947276</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002704531307658722</v>
+        <v>1.080736598798948e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1645952599900465</v>
+        <v>0.1717643672986132</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01004379548228299</v>
+        <v>1.987938854945067e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00683154961625729</v>
+        <v>1.918380384106406e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008437672894910998</v>
+        <v>1.058587134800457e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03144274041876109</v>
+        <v>0.001233192346530124</v>
       </c>
       <c r="M3" t="n">
-        <v>0.05200510847655951</v>
+        <v>0.003287455853390199</v>
       </c>
       <c r="N3" t="n">
-        <v>1.002102685962964</v>
+        <v>1.000008402378887</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0542190736098221</v>
+        <v>0.00342740965504079</v>
       </c>
       <c r="P3" t="n">
-        <v>163.8256533011684</v>
+        <v>174.8705652407799</v>
       </c>
       <c r="Q3" t="n">
-        <v>256.4602159911516</v>
+        <v>267.5051279307631</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_22</t>
+          <t>model_23_6_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9955115190824761</v>
+        <v>0.9999840994070098</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7226712717467861</v>
+        <v>0.7103724354621226</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9438333934092382</v>
+        <v>0.9999913037085953</v>
       </c>
       <c r="E4" t="n">
-        <v>0.98598062328092</v>
+        <v>0.9999562079254539</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9763217218272521</v>
+        <v>0.9999761961142585</v>
       </c>
       <c r="G4" t="n">
-        <v>0.002664556164922007</v>
+        <v>9.439278868797922e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1646343130683808</v>
+        <v>0.1719354335690211</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009890150256703471</v>
+        <v>4.438815071715227e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.006728788601841578</v>
+        <v>1.698755417777107e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008309472852502163</v>
+        <v>1.071318462474315e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03128719268965331</v>
+        <v>0.001176006572536139</v>
       </c>
       <c r="M4" t="n">
-        <v>0.05161933905932937</v>
+        <v>0.003072340942798817</v>
       </c>
       <c r="N4" t="n">
-        <v>1.002071606577319</v>
+        <v>1.000007338735226</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05381688118984768</v>
+        <v>0.00320313685735628</v>
       </c>
       <c r="P4" t="n">
-        <v>163.8554355549544</v>
+        <v>175.141261943484</v>
       </c>
       <c r="Q4" t="n">
-        <v>256.4899982449376</v>
+        <v>267.7758246334672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_21</t>
+          <t>model_23_6_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.995585444801006</v>
+        <v>0.9999856912048752</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7225978257820546</v>
+        <v>0.7101121130646477</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9447941710611026</v>
+        <v>0.9999852916822159</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9862164781733773</v>
+        <v>0.9999609741486204</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9767240713023051</v>
+        <v>0.9999748409496507</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002620670664977916</v>
+        <v>8.494318893799281e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1646779137657459</v>
+        <v>0.1720899721895042</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009720970811531424</v>
+        <v>7.507510917170643e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006615586870847698</v>
+        <v>1.513866998801974e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008168275421853697</v>
+        <v>1.132309045259519e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03111448660344183</v>
+        <v>0.00112427159224118</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05119248641136623</v>
+        <v>0.002914501482895365</v>
       </c>
       <c r="N5" t="n">
-        <v>1.00203748701492</v>
+        <v>1.000006604059288</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05337185654095396</v>
+        <v>0.003038577844872013</v>
       </c>
       <c r="P5" t="n">
-        <v>163.8886500299339</v>
+        <v>175.3522259667183</v>
       </c>
       <c r="Q5" t="n">
-        <v>256.5232127199172</v>
+        <v>267.9867886567015</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_20</t>
+          <t>model_23_6_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9956665071927299</v>
+        <v>0.9999867368638957</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7225151960702291</v>
+        <v>0.7098770728896382</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9458515031065877</v>
+        <v>0.9999785125611306</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9864760377447366</v>
+        <v>0.9999650052991119</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9771668304831412</v>
+        <v>0.9999727339431943</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002572548527537622</v>
+        <v>7.87357052912817e-06</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1647269663321032</v>
+        <v>0.1722295021905968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.009534789494271714</v>
+        <v>1.096775200693017e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.006491007760074196</v>
+        <v>1.357493070225176e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008012896919814287</v>
+        <v>1.227137046950873e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03092264299980457</v>
+        <v>0.001077292062053188</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05072029699772688</v>
+        <v>0.002805988333747696</v>
       </c>
       <c r="N6" t="n">
-        <v>1.002000073603355</v>
+        <v>1.000006121447433</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05287956504640914</v>
+        <v>0.002925445066311942</v>
       </c>
       <c r="P6" t="n">
-        <v>163.9257164529476</v>
+        <v>175.5039978196801</v>
       </c>
       <c r="Q6" t="n">
-        <v>256.5602791429308</v>
+        <v>268.1385605096634</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_19</t>
+          <t>model_23_6_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9957552234346676</v>
+        <v>0.9999873645424057</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7224226571237342</v>
+        <v>0.7096647893553067</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9470130889309663</v>
+        <v>0.9999713022040234</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9867613981444792</v>
+        <v>0.999968426460517</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9776533936940337</v>
+        <v>0.9999701196481339</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002519882733981257</v>
+        <v>7.500953451330398e-06</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1647819014482169</v>
+        <v>0.1723555228667472</v>
       </c>
       <c r="I7" t="n">
-        <v>0.009330250551357368</v>
+        <v>1.464810726536616e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.006354045194356735</v>
+        <v>1.22478146584876e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007842146168326344</v>
+        <v>1.344796096192688e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03070968637306267</v>
+        <v>0.001034694482926283</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05019843358095208</v>
+        <v>0.002738786857594142</v>
       </c>
       <c r="N7" t="n">
-        <v>1.001959127645538</v>
+        <v>1.000005831749659</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05233548482357604</v>
+        <v>0.002855382684192299</v>
       </c>
       <c r="P7" t="n">
-        <v>163.9670858253519</v>
+        <v>175.6009608373158</v>
       </c>
       <c r="Q7" t="n">
-        <v>256.6016485153352</v>
+        <v>268.2355235272991</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_18</t>
+          <t>model_23_6_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9958521870472484</v>
+        <v>0.9999876742329741</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7223184929145062</v>
+        <v>0.709473315084745</v>
       </c>
       <c r="D8" t="n">
-        <v>0.948288500018539</v>
+        <v>0.9999639058753312</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9870747897641911</v>
+        <v>0.9999713401485345</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9781876782599872</v>
+        <v>0.9999671810506227</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002462320944943337</v>
+        <v>7.317107752007938e-06</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1648437378224742</v>
+        <v>0.1724691902650104</v>
       </c>
       <c r="I8" t="n">
-        <v>0.009105668578886299</v>
+        <v>1.842338729523746e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.006203628667225404</v>
+        <v>1.111755459277496e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007654648451477536</v>
+        <v>1.477050712171877e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03047319040576657</v>
+        <v>0.0009962068313106199</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0496217789377138</v>
+        <v>0.002705015296076519</v>
       </c>
       <c r="N8" t="n">
-        <v>1.001914375208962</v>
+        <v>1.00000568881555</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05173428079833543</v>
+        <v>0.0028201733973841</v>
       </c>
       <c r="P8" t="n">
-        <v>164.0133018005502</v>
+        <v>175.6505908478316</v>
       </c>
       <c r="Q8" t="n">
-        <v>256.6478644905334</v>
+        <v>268.2851535378148</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_17</t>
+          <t>model_23_6_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9959579250936158</v>
+        <v>0.9999877458719647</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7222014799079302</v>
+        <v>0.7093004697484997</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9496866814081116</v>
+        <v>0.999956516160194</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9874183915766425</v>
+        <v>0.9999738233875175</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9787734314855819</v>
+        <v>0.99996406085888</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002399550272973864</v>
+        <v>7.27457975251593e-06</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1649132017978764</v>
+        <v>0.1725717987231353</v>
       </c>
       <c r="I9" t="n">
-        <v>0.008859468481206308</v>
+        <v>2.219529159337647e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.006038712351363218</v>
+        <v>1.015427168834963e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.007449088719015802</v>
+        <v>1.617478164086305e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03021034950199678</v>
+        <v>0.0009613540300717656</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04898520463337746</v>
+        <v>0.002697142886929784</v>
       </c>
       <c r="N9" t="n">
-        <v>1.001865573033716</v>
+        <v>1.000005655751401</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05107060620797303</v>
+        <v>0.002811965843481855</v>
       </c>
       <c r="P9" t="n">
-        <v>164.0649478908963</v>
+        <v>175.6622490251049</v>
       </c>
       <c r="Q9" t="n">
-        <v>256.6995105808795</v>
+        <v>268.2968117150881</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_16</t>
+          <t>model_23_6_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9960729668482527</v>
+        <v>0.9999876420063434</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7220696602099814</v>
+        <v>0.7091446555044891</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9512171958212217</v>
+        <v>0.999949270282398</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9877945660027997</v>
+        <v>0.9999759446821236</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9794146501151573</v>
+        <v>0.9999608662392928</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002331256517876362</v>
+        <v>7.336238872081113e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1649914556648933</v>
+        <v>0.1726642967892049</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008589966397414795</v>
+        <v>2.589377754237361e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.005858162371021614</v>
+        <v>9.331392036696305e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007224064384218205</v>
+        <v>1.761255318012206e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02991846498114697</v>
+        <v>0.0009299188656254352</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04828308728609183</v>
+        <v>0.002708549219061953</v>
       </c>
       <c r="N10" t="n">
-        <v>1.001812476839268</v>
+        <v>1.00000570368938</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05033859827163016</v>
+        <v>0.002823857766787253</v>
       </c>
       <c r="P10" t="n">
-        <v>164.1226957574083</v>
+        <v>175.6453685238304</v>
       </c>
       <c r="Q10" t="n">
-        <v>256.7572584473916</v>
+        <v>268.2799312138137</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_15</t>
+          <t>model_23_6_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9961977046246905</v>
+        <v>0.9999874124432642</v>
       </c>
       <c r="C11" t="n">
-        <v>0.721921257215995</v>
+        <v>0.7090040699591503</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9528882316221279</v>
+        <v>0.9999422686214514</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9882054575991192</v>
+        <v>0.9999777664733649</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9801148690885318</v>
+        <v>0.9999576807953264</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002257206785391548</v>
+        <v>7.472517432497592e-06</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1650795540927992</v>
+        <v>0.1727477544418973</v>
       </c>
       <c r="I11" t="n">
-        <v>0.008295720471615683</v>
+        <v>2.946760881032544e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.005660949417456881</v>
+        <v>8.624693901608442e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0.006978334922489019</v>
+        <v>1.904619513648677e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02959443244563081</v>
+        <v>0.0009014253601793007</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04751007035767835</v>
+        <v>0.002733590575140614</v>
       </c>
       <c r="N11" t="n">
-        <v>1.001754905557835</v>
+        <v>1.00000580964157</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0495326724122085</v>
+        <v>0.002849965185236935</v>
       </c>
       <c r="P11" t="n">
-        <v>164.1872543315276</v>
+        <v>175.6085572198082</v>
       </c>
       <c r="Q11" t="n">
-        <v>256.8218170215108</v>
+        <v>268.2431199097915</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_14</t>
+          <t>model_23_6_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9963325218662191</v>
+        <v>0.9999870968354225</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7217537179430635</v>
+        <v>0.7088773963499184</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9547089536822875</v>
+        <v>0.9999355758199062</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9886533384059042</v>
+        <v>0.9999793345331357</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9808779411928844</v>
+        <v>0.9999545614117396</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002177173447018582</v>
+        <v>7.659875880843768e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>0.165179012642531</v>
+        <v>0.1728229533683524</v>
       </c>
       <c r="I12" t="n">
-        <v>0.007975116898715554</v>
+        <v>3.288379014422795e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.005445982994336401</v>
+        <v>8.016421729370878e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>0.006710548266324253</v>
+        <v>2.045010593679941e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.02923464718575955</v>
+        <v>0.0008756964555200245</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04666019124498507</v>
+        <v>0.002767648077491748</v>
       </c>
       <c r="N12" t="n">
-        <v>1.001692682215591</v>
+        <v>1.000005955306728</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04864661218619556</v>
+        <v>0.002885472585971906</v>
       </c>
       <c r="P12" t="n">
-        <v>164.2594556548196</v>
+        <v>175.5590295557765</v>
       </c>
       <c r="Q12" t="n">
-        <v>256.8940183448029</v>
+        <v>268.1935922457598</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_13</t>
+          <t>model_23_6_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9964776466407381</v>
+        <v>0.999986723407052</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7215646252474304</v>
+        <v>0.7087631922935241</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9566872036406343</v>
+        <v>0.9999292395667416</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9891403939563584</v>
+        <v>0.9999806873054133</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9817073018208322</v>
+        <v>0.9999515514422677</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002091021111800267</v>
+        <v>7.881559092920961e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>0.165291266235038</v>
+        <v>0.1728907498295864</v>
       </c>
       <c r="I13" t="n">
-        <v>0.007626774876276454</v>
+        <v>3.611797983915172e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.005212214125574925</v>
+        <v>7.491662567045956e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>0.006419498825457463</v>
+        <v>2.18047737846002e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02883536648285853</v>
+        <v>0.0008524855483678318</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04572768430393417</v>
+        <v>0.002807411457717048</v>
       </c>
       <c r="N13" t="n">
-        <v>1.001625701550429</v>
+        <v>1.000006127658284</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04767440649410863</v>
+        <v>0.002926928775614942</v>
       </c>
       <c r="P13" t="n">
-        <v>164.3402055241553</v>
+        <v>175.501969638467</v>
       </c>
       <c r="Q13" t="n">
-        <v>256.9747682141385</v>
+        <v>268.1365323284502</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9966332249758301</v>
+        <v>0.9999863143117402</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7213505603743549</v>
+        <v>0.7086602343642896</v>
       </c>
       <c r="D14" t="n">
-        <v>0.958831909694567</v>
+        <v>0.9999232753198203</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9896684530522726</v>
+        <v>0.9999818572049478</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9826064923009707</v>
+        <v>0.999948673294259</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001998663091455523</v>
+        <v>8.124415741970095e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1654183443908166</v>
+        <v>0.172951870103931</v>
       </c>
       <c r="I14" t="n">
-        <v>0.007249122274181298</v>
+        <v>3.916228779688698e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00495876505313149</v>
+        <v>7.037842282628769e-06</v>
       </c>
       <c r="K14" t="n">
-        <v>0.006103943833264711</v>
+        <v>2.310011402145053e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02839188190028196</v>
+        <v>0.0008315759829214691</v>
       </c>
       <c r="M14" t="n">
-        <v>0.04470640995937297</v>
+        <v>0.002850336075267282</v>
       </c>
       <c r="N14" t="n">
-        <v>1.001553896165001</v>
+        <v>1.000006316471505</v>
       </c>
       <c r="O14" t="n">
-        <v>0.04660965438637013</v>
+        <v>0.002971680783000498</v>
       </c>
       <c r="P14" t="n">
-        <v>164.4305535524192</v>
+        <v>175.4412734820293</v>
       </c>
       <c r="Q14" t="n">
-        <v>257.0651162424024</v>
+        <v>268.0758361720125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_11</t>
+          <t>model_23_6_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9967990568358261</v>
+        <v>0.999985888999514</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7211078651395348</v>
+        <v>0.7085674614119495</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9611479417557609</v>
+        <v>0.9999177087024591</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9902392100864842</v>
+        <v>0.9999828735548787</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9835778709144942</v>
+        <v>0.9999459547773929</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00190021813579851</v>
+        <v>8.376899451963518e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1655624187660941</v>
+        <v>0.1730069441360229</v>
       </c>
       <c r="I15" t="n">
-        <v>0.006841301569408349</v>
+        <v>4.200363520483744e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.004684822530351797</v>
+        <v>6.643586022959975e-06</v>
       </c>
       <c r="K15" t="n">
-        <v>0.005763055692679199</v>
+        <v>2.432361061389871e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02789954742702644</v>
+        <v>0.0008126136899243439</v>
       </c>
       <c r="M15" t="n">
-        <v>0.04359149155280776</v>
+        <v>0.002894287382407545</v>
       </c>
       <c r="N15" t="n">
-        <v>1.001477358383465</v>
+        <v>1.000006512769455</v>
       </c>
       <c r="O15" t="n">
-        <v>0.04544727159503817</v>
+        <v>0.00301750318827747</v>
       </c>
       <c r="P15" t="n">
-        <v>164.5315731821694</v>
+        <v>175.380065411468</v>
       </c>
       <c r="Q15" t="n">
-        <v>257.1661358721527</v>
+        <v>268.0146281014512</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_10</t>
+          <t>model_23_6_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9969745800136168</v>
+        <v>0.9999854578172191</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7208326714010008</v>
+        <v>0.7084839002637298</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9636382603297422</v>
+        <v>0.9999125237853076</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9908534173773422</v>
+        <v>0.999983756150477</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9846226560568869</v>
+        <v>0.9999433949577674</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001796019995255471</v>
+        <v>8.632867888296257e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1657257856570384</v>
+        <v>0.1730565496432598</v>
       </c>
       <c r="I16" t="n">
-        <v>0.006402791458530711</v>
+        <v>4.465015282103319e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.004390025471915623</v>
+        <v>6.301214927323885e-06</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00539640682935931</v>
+        <v>2.547568387417854e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02735339464397693</v>
+        <v>0.0007956345738561482</v>
       </c>
       <c r="M16" t="n">
-        <v>0.04237947610878963</v>
+        <v>0.002938174244032552</v>
       </c>
       <c r="N16" t="n">
-        <v>1.001396347686023</v>
+        <v>1.000006711776668</v>
       </c>
       <c r="O16" t="n">
-        <v>0.04418365814435034</v>
+        <v>0.003063258404460181</v>
       </c>
       <c r="P16" t="n">
-        <v>164.6443643518967</v>
+        <v>175.3198675838656</v>
       </c>
       <c r="Q16" t="n">
-        <v>257.27892704188</v>
+        <v>267.9544302738488</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_9</t>
+          <t>model_23_6_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9971590599807949</v>
+        <v>0.9999850307498844</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7205195263632846</v>
+        <v>0.7084085557115658</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9663060447607792</v>
+        <v>0.9999077185632308</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9915117568501219</v>
+        <v>0.9999845225316929</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9857421617690864</v>
+        <v>0.999941000366152</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001686504717618939</v>
+        <v>8.886393506548346e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1659116820785879</v>
+        <v>0.1731012774241395</v>
       </c>
       <c r="I17" t="n">
-        <v>0.005933032103693893</v>
+        <v>4.710286411882472e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.004074046578606212</v>
+        <v>6.003925005307461e-06</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00500353610388366</v>
+        <v>2.655339456206609e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02674674970877325</v>
+        <v>0.0007802301341698738</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0410670758347723</v>
+        <v>0.002981005452284237</v>
       </c>
       <c r="N17" t="n">
-        <v>1.001311203085787</v>
+        <v>1.000006908884669</v>
       </c>
       <c r="O17" t="n">
-        <v>0.04281538627362501</v>
+        <v>0.003107913025919964</v>
       </c>
       <c r="P17" t="n">
-        <v>164.7701942123656</v>
+        <v>175.2619785411042</v>
       </c>
       <c r="Q17" t="n">
-        <v>257.4047569023488</v>
+        <v>267.8965412310875</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_8</t>
+          <t>model_23_6_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9973509899399806</v>
+        <v>0.9999846165098382</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7201625931795006</v>
+        <v>0.7083407440451204</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9691467950928072</v>
+        <v>0.9999032919209467</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9922135841186828</v>
+        <v>0.999985194245996</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9869347775199883</v>
+        <v>0.9999387797750316</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001572566802903737</v>
+        <v>9.132304292218987e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1661235730351929</v>
+        <v>0.173141533358653</v>
       </c>
       <c r="I18" t="n">
-        <v>0.005432815883934627</v>
+        <v>4.936233836753097e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.003737195132227245</v>
+        <v>5.743357694119971e-06</v>
       </c>
       <c r="K18" t="n">
-        <v>0.004585008703652681</v>
+        <v>2.755279453008102e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.02607309478714911</v>
+        <v>0.0007663705434874727</v>
       </c>
       <c r="M18" t="n">
-        <v>0.03965560241509056</v>
+        <v>0.003021970266600746</v>
       </c>
       <c r="N18" t="n">
-        <v>1.001222620027701</v>
+        <v>1.000007100072382</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04134382350831464</v>
+        <v>0.003150621797190783</v>
       </c>
       <c r="P18" t="n">
-        <v>164.9100921766365</v>
+        <v>175.2073850166422</v>
       </c>
       <c r="Q18" t="n">
-        <v>257.5446548666197</v>
+        <v>267.8419477066255</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_7</t>
+          <t>model_23_6_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9975481118771349</v>
+        <v>0.9999842166614159</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7197552480231568</v>
+        <v>0.7082796464909251</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9721508512163155</v>
+        <v>0.9998992043264463</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9929565753712778</v>
+        <v>0.9999857825721488</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9881965364843407</v>
+        <v>0.9999367152712642</v>
       </c>
       <c r="G19" t="n">
-        <v>0.001455546705784704</v>
+        <v>9.369671588212998e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1663653907163931</v>
+        <v>0.1731778035061002</v>
       </c>
       <c r="I19" t="n">
-        <v>0.004903843808809223</v>
+        <v>5.144875374059385e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.003380586477512565</v>
+        <v>5.515137805054753e-06</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00414221671581487</v>
+        <v>2.84819457728243e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02532538434295219</v>
+        <v>0.0007538875981464416</v>
       </c>
       <c r="M19" t="n">
-        <v>0.03815162782614529</v>
+        <v>0.003060991928805595</v>
       </c>
       <c r="N19" t="n">
-        <v>1.001131640672092</v>
+        <v>1.000007284617808</v>
       </c>
       <c r="O19" t="n">
-        <v>0.03977582160746138</v>
+        <v>0.003191304692341669</v>
       </c>
       <c r="P19" t="n">
-        <v>165.0647474122499</v>
+        <v>175.1560650232235</v>
       </c>
       <c r="Q19" t="n">
-        <v>257.6993101022332</v>
+        <v>267.7906277132067</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_6</t>
+          <t>model_23_6_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9977473647264978</v>
+        <v>0.9999838370602888</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7192890432484356</v>
+        <v>0.7082246704801816</v>
       </c>
       <c r="D20" t="n">
-        <v>0.975301854871892</v>
+        <v>0.9998954631562342</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9937371801527323</v>
+        <v>0.9999862940836466</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9895208923985346</v>
+        <v>0.9999348142273234</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001337261607127926</v>
+        <v>9.595019215187408e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1666421500096653</v>
+        <v>0.1732104396409176</v>
       </c>
       <c r="I20" t="n">
-        <v>0.004348996337959889</v>
+        <v>5.335834507678673e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.003005924703223716</v>
+        <v>5.316715387949254e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00367745743577946</v>
+        <v>2.933753023236799e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02449525351571977</v>
+        <v>0.0007426512499303392</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03656858771032764</v>
+        <v>0.003097582801990515</v>
       </c>
       <c r="N20" t="n">
-        <v>1.00103967781854</v>
+        <v>1.000007459818328</v>
       </c>
       <c r="O20" t="n">
-        <v>0.03812538819656856</v>
+        <v>0.00322945331475162</v>
       </c>
       <c r="P20" t="n">
-        <v>165.2342626654834</v>
+        <v>175.1085328517631</v>
       </c>
       <c r="Q20" t="n">
-        <v>257.8688253554666</v>
+        <v>267.7430955417464</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_5</t>
+          <t>model_23_6_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9979444676064523</v>
+        <v>0.9999834794676473</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7187542952518812</v>
+        <v>0.7081751378691399</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9785737428057425</v>
+        <v>0.9998920365063146</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9945494588914618</v>
+        <v>0.9999867495329042</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9908972013853251</v>
+        <v>0.9999330673761327</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001220252823185899</v>
+        <v>9.807301654369018e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1669595995203306</v>
+        <v>0.1732398443385293</v>
       </c>
       <c r="I21" t="n">
-        <v>0.003772862844180355</v>
+        <v>5.510739701175431e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.002616060586708228</v>
+        <v>5.140040292735668e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00319446614397373</v>
+        <v>3.012371865224499e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02357332281412302</v>
+        <v>0.000732440720730705</v>
       </c>
       <c r="M21" t="n">
-        <v>0.03493211735904222</v>
+        <v>0.003131661165319297</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000948707258561</v>
+        <v>1.000007624861086</v>
       </c>
       <c r="O21" t="n">
-        <v>0.03641924991446829</v>
+        <v>0.003264982464559246</v>
       </c>
       <c r="P21" t="n">
-        <v>165.417394419174</v>
+        <v>175.0647667658797</v>
       </c>
       <c r="Q21" t="n">
-        <v>258.0519571091572</v>
+        <v>267.699329455863</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_4</t>
+          <t>model_23_6_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9981336358695565</v>
+        <v>0.9999831438601282</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7181390699169045</v>
+        <v>0.7081304690161236</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9819272009283739</v>
+        <v>0.9998889053444551</v>
       </c>
       <c r="E22" t="n">
-        <v>0.99538471931913</v>
+        <v>0.9999871463322039</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9923097282985365</v>
+        <v>0.9999314626968524</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001107954370563748</v>
+        <v>1.000653277525527e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1673248238555234</v>
+        <v>0.1732663616992738</v>
       </c>
       <c r="I22" t="n">
-        <v>0.00318236598625121</v>
+        <v>5.670562409589396e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.002215166099179882</v>
+        <v>4.986116331151812e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>0.002698764811591049</v>
+        <v>3.084592113548734e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02254866942859946</v>
+        <v>0.0007233189139314569</v>
       </c>
       <c r="M22" t="n">
-        <v>0.03328594854535091</v>
+        <v>0.003163310413989635</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000861398829435</v>
+        <v>1.000007779756864</v>
       </c>
       <c r="O22" t="n">
-        <v>0.03470300028633892</v>
+        <v>0.003297979087268457</v>
       </c>
       <c r="P22" t="n">
-        <v>165.6104797466134</v>
+        <v>175.0245448014751</v>
       </c>
       <c r="Q22" t="n">
-        <v>258.2450424365967</v>
+        <v>267.6591074914584</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_3</t>
+          <t>model_23_6_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.998307181099953</v>
+        <v>0.9999828304663386</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7174290037572639</v>
+        <v>0.7080902640210169</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9853076639334034</v>
+        <v>0.9998860420746001</v>
       </c>
       <c r="E23" t="n">
-        <v>0.996230054772665</v>
+        <v>0.9999874999720263</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9937358923214306</v>
+        <v>0.9999299915559229</v>
       </c>
       <c r="G23" t="n">
-        <v>0.001004930425036784</v>
+        <v>1.01925768666136e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1677463498011471</v>
+        <v>0.1732902291211345</v>
       </c>
       <c r="I23" t="n">
-        <v>0.00258711394796147</v>
+        <v>5.816711207915819e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.001809435967344721</v>
+        <v>4.848934530443534e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>0.00219827777680772</v>
+        <v>3.150802330480086e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02140898010582652</v>
+        <v>0.0007150465813852122</v>
       </c>
       <c r="M23" t="n">
-        <v>0.03170063761246427</v>
+        <v>0.003192581536408052</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000781301030791</v>
+        <v>1.000007924400151</v>
       </c>
       <c r="O23" t="n">
-        <v>0.03305019938499326</v>
+        <v>0.003328496341967803</v>
       </c>
       <c r="P23" t="n">
-        <v>165.8056739373733</v>
+        <v>174.9877017215874</v>
       </c>
       <c r="Q23" t="n">
-        <v>258.4402366273566</v>
+        <v>267.6222644115707</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_2</t>
+          <t>model_23_6_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9984547241614634</v>
+        <v>0.9999825404620331</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7166069331183824</v>
+        <v>0.7080541537833718</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9886344905054552</v>
+        <v>0.9998834429552309</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9970676185822492</v>
+        <v>0.9999878105980111</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9951433170353889</v>
+        <v>0.9999286515549929</v>
       </c>
       <c r="G24" t="n">
-        <v>0.000917342490195827</v>
+        <v>1.036473594997633e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1682343664439896</v>
+        <v>0.1733116657180817</v>
       </c>
       <c r="I24" t="n">
-        <v>0.002001306531905158</v>
+        <v>5.949377073078478e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.001407435940654859</v>
+        <v>4.728438395002441e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00170436697099422</v>
+        <v>3.211110456289361e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02014075377625237</v>
+        <v>0.0007077014977150002</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03028766234287201</v>
+        <v>0.003219430997859145</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000713204233171</v>
+        <v>1.000008058248292</v>
       </c>
       <c r="O24" t="n">
-        <v>0.03157707083291243</v>
+        <v>0.003356488840578916</v>
       </c>
       <c r="P24" t="n">
-        <v>165.9880593311682</v>
+        <v>174.9542025751202</v>
       </c>
       <c r="Q24" t="n">
-        <v>258.6226220211515</v>
+        <v>267.5887652651035</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_1</t>
+          <t>model_23_6_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9985628080260398</v>
+        <v>0.9999822711794261</v>
       </c>
       <c r="C25" t="n">
-        <v>0.715651903249341</v>
+        <v>0.7080215203323313</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9918004583997146</v>
+        <v>0.9998810694421522</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9978728733405384</v>
+        <v>0.9999880855958372</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9964882548258959</v>
+        <v>0.9999274241330882</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0008531792392034326</v>
+        <v>1.052459373788318e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1688013134293948</v>
+        <v>0.1733310383443109</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001443824068877462</v>
+        <v>6.070527401838159e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.001020943078116934</v>
+        <v>4.621762917369385e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.001232384845563175</v>
+        <v>3.266351846787549e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01872772953289324</v>
+        <v>0.0007009914350087078</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02920923208856119</v>
+        <v>0.003244163025786957</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000663319372597</v>
+        <v>1.000008182532573</v>
       </c>
       <c r="O25" t="n">
-        <v>0.03045272957001721</v>
+        <v>0.00338227376213797</v>
       </c>
       <c r="P25" t="n">
-        <v>166.1330818090472</v>
+        <v>174.9235915577338</v>
       </c>
       <c r="Q25" t="n">
-        <v>258.7676444990305</v>
+        <v>267.558154247717</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_0</t>
+          <t>model_23_6_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9986138377580389</v>
+        <v>0.9999820243005419</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7145367154927298</v>
+        <v>0.7079922207446547</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9946602525369039</v>
+        <v>0.9998789194898206</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9986128885085277</v>
+        <v>0.99998833155263</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9977117876742508</v>
+        <v>0.9999263108496301</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0008228857859191012</v>
+        <v>1.067115170806465e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.169463337055322</v>
+        <v>0.173348431845232</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0009402545026025727</v>
+        <v>6.180266604092836e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0006657628352763536</v>
+        <v>4.526352860045083e-06</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0008030076369090545</v>
+        <v>3.31645631862004e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0171526815298173</v>
+        <v>0.0006949148305250913</v>
       </c>
       <c r="M26" t="n">
-        <v>0.02868598588020117</v>
+        <v>0.003266672880480176</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000639767188597</v>
+        <v>1.000008296476673</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02990720768729834</v>
+        <v>0.003405741907947302</v>
       </c>
       <c r="P26" t="n">
-        <v>166.2053862893176</v>
+        <v>174.8959331191509</v>
       </c>
       <c r="Q26" t="n">
-        <v>258.8399489793009</v>
+        <v>267.5304958091342</v>
       </c>
     </row>
   </sheetData>
